--- a/artfynd/A 27430-2024 artfynd.xlsx
+++ b/artfynd/A 27430-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>119132897</v>
       </c>
       <c r="B2" t="n">
-        <v>74448</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,16 +794,11 @@
         <v>119132865</v>
       </c>
       <c r="B3" t="n">
-        <v>57324</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -913,12 +903,7 @@
         <v>119132873</v>
       </c>
       <c r="B4" t="n">
-        <v>9378</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>9403</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
